--- a/mass_production_tool/value_test_sample.xlsx
+++ b/mass_production_tool/value_test_sample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\Mass_produc\mass_produc\mass_production_tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D75C271-66D2-41B0-AFBC-189AA630FB92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70369499-BE07-45AD-A22D-4F0A417781BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3048" yWindow="6600" windowWidth="34560" windowHeight="18600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8880" yWindow="6600" windowWidth="34560" windowHeight="18600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ValueTest" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="28">
   <si>
     <t>HDR</t>
   </si>
@@ -316,7 +316,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S16"/>
+  <dimension ref="A1:S61"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <sheetData>
     <row r="1" spans="1:19">
@@ -1080,6 +1080,2121 @@
         <v>27</v>
       </c>
       <c r="O16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
+      <c r="A17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17">
+        <v>8</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>10</v>
+      </c>
+      <c r="E17">
+        <v>20</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>2</v>
+      </c>
+      <c r="I17">
+        <v>3</v>
+      </c>
+      <c r="J17">
+        <v>4</v>
+      </c>
+      <c r="K17">
+        <v>5</v>
+      </c>
+      <c r="L17">
+        <v>6</v>
+      </c>
+      <c r="M17">
+        <v>7</v>
+      </c>
+      <c r="N17" t="s">
+        <v>20</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
+      <c r="A18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18">
+        <v>8</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>10</v>
+      </c>
+      <c r="E18">
+        <v>21</v>
+      </c>
+      <c r="F18">
+        <v>10</v>
+      </c>
+      <c r="G18">
+        <v>11</v>
+      </c>
+      <c r="H18">
+        <v>12</v>
+      </c>
+      <c r="I18">
+        <v>13</v>
+      </c>
+      <c r="J18">
+        <v>14</v>
+      </c>
+      <c r="K18">
+        <v>15</v>
+      </c>
+      <c r="L18">
+        <v>16</v>
+      </c>
+      <c r="M18">
+        <v>17</v>
+      </c>
+      <c r="N18">
+        <v>14</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19">
+        <v>8</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19">
+        <v>20</v>
+      </c>
+      <c r="E19">
+        <v>30</v>
+      </c>
+      <c r="F19">
+        <v>80</v>
+      </c>
+      <c r="G19">
+        <v>81</v>
+      </c>
+      <c r="H19">
+        <v>82</v>
+      </c>
+      <c r="I19">
+        <v>83</v>
+      </c>
+      <c r="J19">
+        <v>84</v>
+      </c>
+      <c r="K19">
+        <v>85</v>
+      </c>
+      <c r="L19">
+        <v>86</v>
+      </c>
+      <c r="M19">
+        <v>87</v>
+      </c>
+      <c r="N19">
+        <v>32</v>
+      </c>
+      <c r="O19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>8</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+      <c r="D20">
+        <v>20</v>
+      </c>
+      <c r="E20">
+        <v>31</v>
+      </c>
+      <c r="F20">
+        <v>90</v>
+      </c>
+      <c r="G20">
+        <v>91</v>
+      </c>
+      <c r="H20">
+        <v>92</v>
+      </c>
+      <c r="I20">
+        <v>93</v>
+      </c>
+      <c r="J20">
+        <v>94</v>
+      </c>
+      <c r="K20">
+        <v>95</v>
+      </c>
+      <c r="L20">
+        <v>96</v>
+      </c>
+      <c r="M20">
+        <v>97</v>
+      </c>
+      <c r="N20">
+        <v>64</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
+      <c r="A21" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21">
+        <v>8</v>
+      </c>
+      <c r="C21">
+        <v>3</v>
+      </c>
+      <c r="D21">
+        <v>30</v>
+      </c>
+      <c r="E21">
+        <v>40</v>
+      </c>
+      <c r="F21" t="s">
+        <v>21</v>
+      </c>
+      <c r="G21" t="s">
+        <v>22</v>
+      </c>
+      <c r="H21" t="s">
+        <v>23</v>
+      </c>
+      <c r="I21" t="s">
+        <v>24</v>
+      </c>
+      <c r="J21" t="s">
+        <v>25</v>
+      </c>
+      <c r="K21" t="s">
+        <v>26</v>
+      </c>
+      <c r="L21">
+        <v>12</v>
+      </c>
+      <c r="M21">
+        <v>34</v>
+      </c>
+      <c r="N21" t="s">
+        <v>27</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
+      <c r="A22" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22">
+        <v>8</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>10</v>
+      </c>
+      <c r="E22">
+        <v>20</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22">
+        <v>2</v>
+      </c>
+      <c r="I22">
+        <v>3</v>
+      </c>
+      <c r="J22">
+        <v>4</v>
+      </c>
+      <c r="K22">
+        <v>5</v>
+      </c>
+      <c r="L22">
+        <v>6</v>
+      </c>
+      <c r="M22">
+        <v>7</v>
+      </c>
+      <c r="N22" t="s">
+        <v>20</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
+      <c r="A23" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23">
+        <v>8</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>10</v>
+      </c>
+      <c r="E23">
+        <v>21</v>
+      </c>
+      <c r="F23">
+        <v>10</v>
+      </c>
+      <c r="G23">
+        <v>11</v>
+      </c>
+      <c r="H23">
+        <v>12</v>
+      </c>
+      <c r="I23">
+        <v>13</v>
+      </c>
+      <c r="J23">
+        <v>14</v>
+      </c>
+      <c r="K23">
+        <v>15</v>
+      </c>
+      <c r="L23">
+        <v>16</v>
+      </c>
+      <c r="M23">
+        <v>17</v>
+      </c>
+      <c r="N23">
+        <v>14</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
+      <c r="A24" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24">
+        <v>8</v>
+      </c>
+      <c r="C24">
+        <v>2</v>
+      </c>
+      <c r="D24">
+        <v>20</v>
+      </c>
+      <c r="E24">
+        <v>30</v>
+      </c>
+      <c r="F24">
+        <v>80</v>
+      </c>
+      <c r="G24">
+        <v>81</v>
+      </c>
+      <c r="H24">
+        <v>82</v>
+      </c>
+      <c r="I24">
+        <v>83</v>
+      </c>
+      <c r="J24">
+        <v>84</v>
+      </c>
+      <c r="K24">
+        <v>85</v>
+      </c>
+      <c r="L24">
+        <v>86</v>
+      </c>
+      <c r="M24">
+        <v>87</v>
+      </c>
+      <c r="N24">
+        <v>32</v>
+      </c>
+      <c r="O24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15">
+      <c r="A25" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25">
+        <v>8</v>
+      </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
+      <c r="D25">
+        <v>20</v>
+      </c>
+      <c r="E25">
+        <v>31</v>
+      </c>
+      <c r="F25">
+        <v>90</v>
+      </c>
+      <c r="G25">
+        <v>91</v>
+      </c>
+      <c r="H25">
+        <v>92</v>
+      </c>
+      <c r="I25">
+        <v>93</v>
+      </c>
+      <c r="J25">
+        <v>94</v>
+      </c>
+      <c r="K25">
+        <v>95</v>
+      </c>
+      <c r="L25">
+        <v>96</v>
+      </c>
+      <c r="M25">
+        <v>97</v>
+      </c>
+      <c r="N25">
+        <v>64</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15">
+      <c r="A26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26">
+        <v>8</v>
+      </c>
+      <c r="C26">
+        <v>3</v>
+      </c>
+      <c r="D26">
+        <v>30</v>
+      </c>
+      <c r="E26">
+        <v>40</v>
+      </c>
+      <c r="F26" t="s">
+        <v>21</v>
+      </c>
+      <c r="G26" t="s">
+        <v>22</v>
+      </c>
+      <c r="H26" t="s">
+        <v>23</v>
+      </c>
+      <c r="I26" t="s">
+        <v>24</v>
+      </c>
+      <c r="J26" t="s">
+        <v>25</v>
+      </c>
+      <c r="K26" t="s">
+        <v>26</v>
+      </c>
+      <c r="L26">
+        <v>12</v>
+      </c>
+      <c r="M26">
+        <v>34</v>
+      </c>
+      <c r="N26" t="s">
+        <v>27</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15">
+      <c r="A27" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27">
+        <v>8</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
+        <v>10</v>
+      </c>
+      <c r="E27">
+        <v>20</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27">
+        <v>2</v>
+      </c>
+      <c r="I27">
+        <v>3</v>
+      </c>
+      <c r="J27">
+        <v>4</v>
+      </c>
+      <c r="K27">
+        <v>5</v>
+      </c>
+      <c r="L27">
+        <v>6</v>
+      </c>
+      <c r="M27">
+        <v>7</v>
+      </c>
+      <c r="N27" t="s">
+        <v>20</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15">
+      <c r="A28" t="s">
+        <v>19</v>
+      </c>
+      <c r="B28">
+        <v>8</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28">
+        <v>10</v>
+      </c>
+      <c r="E28">
+        <v>21</v>
+      </c>
+      <c r="F28">
+        <v>10</v>
+      </c>
+      <c r="G28">
+        <v>11</v>
+      </c>
+      <c r="H28">
+        <v>12</v>
+      </c>
+      <c r="I28">
+        <v>13</v>
+      </c>
+      <c r="J28">
+        <v>14</v>
+      </c>
+      <c r="K28">
+        <v>15</v>
+      </c>
+      <c r="L28">
+        <v>16</v>
+      </c>
+      <c r="M28">
+        <v>17</v>
+      </c>
+      <c r="N28">
+        <v>14</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15">
+      <c r="A29" t="s">
+        <v>19</v>
+      </c>
+      <c r="B29">
+        <v>8</v>
+      </c>
+      <c r="C29">
+        <v>2</v>
+      </c>
+      <c r="D29">
+        <v>20</v>
+      </c>
+      <c r="E29">
+        <v>30</v>
+      </c>
+      <c r="F29">
+        <v>80</v>
+      </c>
+      <c r="G29">
+        <v>81</v>
+      </c>
+      <c r="H29">
+        <v>82</v>
+      </c>
+      <c r="I29">
+        <v>83</v>
+      </c>
+      <c r="J29">
+        <v>84</v>
+      </c>
+      <c r="K29">
+        <v>85</v>
+      </c>
+      <c r="L29">
+        <v>86</v>
+      </c>
+      <c r="M29">
+        <v>87</v>
+      </c>
+      <c r="N29">
+        <v>32</v>
+      </c>
+      <c r="O29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15">
+      <c r="A30" t="s">
+        <v>19</v>
+      </c>
+      <c r="B30">
+        <v>8</v>
+      </c>
+      <c r="C30">
+        <v>2</v>
+      </c>
+      <c r="D30">
+        <v>20</v>
+      </c>
+      <c r="E30">
+        <v>31</v>
+      </c>
+      <c r="F30">
+        <v>90</v>
+      </c>
+      <c r="G30">
+        <v>91</v>
+      </c>
+      <c r="H30">
+        <v>92</v>
+      </c>
+      <c r="I30">
+        <v>93</v>
+      </c>
+      <c r="J30">
+        <v>94</v>
+      </c>
+      <c r="K30">
+        <v>95</v>
+      </c>
+      <c r="L30">
+        <v>96</v>
+      </c>
+      <c r="M30">
+        <v>97</v>
+      </c>
+      <c r="N30">
+        <v>64</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15">
+      <c r="A31" t="s">
+        <v>19</v>
+      </c>
+      <c r="B31">
+        <v>8</v>
+      </c>
+      <c r="C31">
+        <v>3</v>
+      </c>
+      <c r="D31">
+        <v>30</v>
+      </c>
+      <c r="E31">
+        <v>40</v>
+      </c>
+      <c r="F31" t="s">
+        <v>21</v>
+      </c>
+      <c r="G31" t="s">
+        <v>22</v>
+      </c>
+      <c r="H31" t="s">
+        <v>23</v>
+      </c>
+      <c r="I31" t="s">
+        <v>24</v>
+      </c>
+      <c r="J31" t="s">
+        <v>25</v>
+      </c>
+      <c r="K31" t="s">
+        <v>26</v>
+      </c>
+      <c r="L31">
+        <v>12</v>
+      </c>
+      <c r="M31">
+        <v>34</v>
+      </c>
+      <c r="N31" t="s">
+        <v>27</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15">
+      <c r="A32" t="s">
+        <v>19</v>
+      </c>
+      <c r="B32">
+        <v>8</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32">
+        <v>10</v>
+      </c>
+      <c r="E32">
+        <v>20</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+      <c r="H32">
+        <v>2</v>
+      </c>
+      <c r="I32">
+        <v>3</v>
+      </c>
+      <c r="J32">
+        <v>4</v>
+      </c>
+      <c r="K32">
+        <v>5</v>
+      </c>
+      <c r="L32">
+        <v>6</v>
+      </c>
+      <c r="M32">
+        <v>7</v>
+      </c>
+      <c r="N32" t="s">
+        <v>20</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15">
+      <c r="A33" t="s">
+        <v>19</v>
+      </c>
+      <c r="B33">
+        <v>8</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33">
+        <v>10</v>
+      </c>
+      <c r="E33">
+        <v>21</v>
+      </c>
+      <c r="F33">
+        <v>10</v>
+      </c>
+      <c r="G33">
+        <v>11</v>
+      </c>
+      <c r="H33">
+        <v>12</v>
+      </c>
+      <c r="I33">
+        <v>13</v>
+      </c>
+      <c r="J33">
+        <v>14</v>
+      </c>
+      <c r="K33">
+        <v>15</v>
+      </c>
+      <c r="L33">
+        <v>16</v>
+      </c>
+      <c r="M33">
+        <v>17</v>
+      </c>
+      <c r="N33">
+        <v>14</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15">
+      <c r="A34" t="s">
+        <v>19</v>
+      </c>
+      <c r="B34">
+        <v>8</v>
+      </c>
+      <c r="C34">
+        <v>2</v>
+      </c>
+      <c r="D34">
+        <v>20</v>
+      </c>
+      <c r="E34">
+        <v>30</v>
+      </c>
+      <c r="F34">
+        <v>80</v>
+      </c>
+      <c r="G34">
+        <v>81</v>
+      </c>
+      <c r="H34">
+        <v>82</v>
+      </c>
+      <c r="I34">
+        <v>83</v>
+      </c>
+      <c r="J34">
+        <v>84</v>
+      </c>
+      <c r="K34">
+        <v>85</v>
+      </c>
+      <c r="L34">
+        <v>86</v>
+      </c>
+      <c r="M34">
+        <v>87</v>
+      </c>
+      <c r="N34">
+        <v>32</v>
+      </c>
+      <c r="O34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15">
+      <c r="A35" t="s">
+        <v>19</v>
+      </c>
+      <c r="B35">
+        <v>8</v>
+      </c>
+      <c r="C35">
+        <v>2</v>
+      </c>
+      <c r="D35">
+        <v>20</v>
+      </c>
+      <c r="E35">
+        <v>31</v>
+      </c>
+      <c r="F35">
+        <v>90</v>
+      </c>
+      <c r="G35">
+        <v>91</v>
+      </c>
+      <c r="H35">
+        <v>92</v>
+      </c>
+      <c r="I35">
+        <v>93</v>
+      </c>
+      <c r="J35">
+        <v>94</v>
+      </c>
+      <c r="K35">
+        <v>95</v>
+      </c>
+      <c r="L35">
+        <v>96</v>
+      </c>
+      <c r="M35">
+        <v>97</v>
+      </c>
+      <c r="N35">
+        <v>64</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15">
+      <c r="A36" t="s">
+        <v>19</v>
+      </c>
+      <c r="B36">
+        <v>8</v>
+      </c>
+      <c r="C36">
+        <v>3</v>
+      </c>
+      <c r="D36">
+        <v>30</v>
+      </c>
+      <c r="E36">
+        <v>40</v>
+      </c>
+      <c r="F36" t="s">
+        <v>21</v>
+      </c>
+      <c r="G36" t="s">
+        <v>22</v>
+      </c>
+      <c r="H36" t="s">
+        <v>23</v>
+      </c>
+      <c r="I36" t="s">
+        <v>24</v>
+      </c>
+      <c r="J36" t="s">
+        <v>25</v>
+      </c>
+      <c r="K36" t="s">
+        <v>26</v>
+      </c>
+      <c r="L36">
+        <v>12</v>
+      </c>
+      <c r="M36">
+        <v>34</v>
+      </c>
+      <c r="N36" t="s">
+        <v>27</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15">
+      <c r="A37" t="s">
+        <v>19</v>
+      </c>
+      <c r="B37">
+        <v>8</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="D37">
+        <v>10</v>
+      </c>
+      <c r="E37">
+        <v>20</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+      <c r="H37">
+        <v>2</v>
+      </c>
+      <c r="I37">
+        <v>3</v>
+      </c>
+      <c r="J37">
+        <v>4</v>
+      </c>
+      <c r="K37">
+        <v>5</v>
+      </c>
+      <c r="L37">
+        <v>6</v>
+      </c>
+      <c r="M37">
+        <v>7</v>
+      </c>
+      <c r="N37" t="s">
+        <v>20</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15">
+      <c r="A38" t="s">
+        <v>19</v>
+      </c>
+      <c r="B38">
+        <v>8</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+      <c r="D38">
+        <v>10</v>
+      </c>
+      <c r="E38">
+        <v>21</v>
+      </c>
+      <c r="F38">
+        <v>10</v>
+      </c>
+      <c r="G38">
+        <v>11</v>
+      </c>
+      <c r="H38">
+        <v>12</v>
+      </c>
+      <c r="I38">
+        <v>13</v>
+      </c>
+      <c r="J38">
+        <v>14</v>
+      </c>
+      <c r="K38">
+        <v>15</v>
+      </c>
+      <c r="L38">
+        <v>16</v>
+      </c>
+      <c r="M38">
+        <v>17</v>
+      </c>
+      <c r="N38">
+        <v>14</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15">
+      <c r="A39" t="s">
+        <v>19</v>
+      </c>
+      <c r="B39">
+        <v>8</v>
+      </c>
+      <c r="C39">
+        <v>2</v>
+      </c>
+      <c r="D39">
+        <v>20</v>
+      </c>
+      <c r="E39">
+        <v>30</v>
+      </c>
+      <c r="F39">
+        <v>80</v>
+      </c>
+      <c r="G39">
+        <v>81</v>
+      </c>
+      <c r="H39">
+        <v>82</v>
+      </c>
+      <c r="I39">
+        <v>83</v>
+      </c>
+      <c r="J39">
+        <v>84</v>
+      </c>
+      <c r="K39">
+        <v>85</v>
+      </c>
+      <c r="L39">
+        <v>86</v>
+      </c>
+      <c r="M39">
+        <v>87</v>
+      </c>
+      <c r="N39">
+        <v>32</v>
+      </c>
+      <c r="O39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15">
+      <c r="A40" t="s">
+        <v>19</v>
+      </c>
+      <c r="B40">
+        <v>8</v>
+      </c>
+      <c r="C40">
+        <v>2</v>
+      </c>
+      <c r="D40">
+        <v>20</v>
+      </c>
+      <c r="E40">
+        <v>31</v>
+      </c>
+      <c r="F40">
+        <v>90</v>
+      </c>
+      <c r="G40">
+        <v>91</v>
+      </c>
+      <c r="H40">
+        <v>92</v>
+      </c>
+      <c r="I40">
+        <v>93</v>
+      </c>
+      <c r="J40">
+        <v>94</v>
+      </c>
+      <c r="K40">
+        <v>95</v>
+      </c>
+      <c r="L40">
+        <v>96</v>
+      </c>
+      <c r="M40">
+        <v>97</v>
+      </c>
+      <c r="N40">
+        <v>64</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15">
+      <c r="A41" t="s">
+        <v>19</v>
+      </c>
+      <c r="B41">
+        <v>8</v>
+      </c>
+      <c r="C41">
+        <v>3</v>
+      </c>
+      <c r="D41">
+        <v>30</v>
+      </c>
+      <c r="E41">
+        <v>40</v>
+      </c>
+      <c r="F41" t="s">
+        <v>21</v>
+      </c>
+      <c r="G41" t="s">
+        <v>22</v>
+      </c>
+      <c r="H41" t="s">
+        <v>23</v>
+      </c>
+      <c r="I41" t="s">
+        <v>24</v>
+      </c>
+      <c r="J41" t="s">
+        <v>25</v>
+      </c>
+      <c r="K41" t="s">
+        <v>26</v>
+      </c>
+      <c r="L41">
+        <v>12</v>
+      </c>
+      <c r="M41">
+        <v>34</v>
+      </c>
+      <c r="N41" t="s">
+        <v>27</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15">
+      <c r="A42" t="s">
+        <v>19</v>
+      </c>
+      <c r="B42">
+        <v>8</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+      <c r="D42">
+        <v>10</v>
+      </c>
+      <c r="E42">
+        <v>20</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
+      <c r="H42">
+        <v>2</v>
+      </c>
+      <c r="I42">
+        <v>3</v>
+      </c>
+      <c r="J42">
+        <v>4</v>
+      </c>
+      <c r="K42">
+        <v>5</v>
+      </c>
+      <c r="L42">
+        <v>6</v>
+      </c>
+      <c r="M42">
+        <v>7</v>
+      </c>
+      <c r="N42" t="s">
+        <v>20</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15">
+      <c r="A43" t="s">
+        <v>19</v>
+      </c>
+      <c r="B43">
+        <v>8</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+      <c r="D43">
+        <v>10</v>
+      </c>
+      <c r="E43">
+        <v>21</v>
+      </c>
+      <c r="F43">
+        <v>10</v>
+      </c>
+      <c r="G43">
+        <v>11</v>
+      </c>
+      <c r="H43">
+        <v>12</v>
+      </c>
+      <c r="I43">
+        <v>13</v>
+      </c>
+      <c r="J43">
+        <v>14</v>
+      </c>
+      <c r="K43">
+        <v>15</v>
+      </c>
+      <c r="L43">
+        <v>16</v>
+      </c>
+      <c r="M43">
+        <v>17</v>
+      </c>
+      <c r="N43">
+        <v>14</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15">
+      <c r="A44" t="s">
+        <v>19</v>
+      </c>
+      <c r="B44">
+        <v>8</v>
+      </c>
+      <c r="C44">
+        <v>2</v>
+      </c>
+      <c r="D44">
+        <v>20</v>
+      </c>
+      <c r="E44">
+        <v>30</v>
+      </c>
+      <c r="F44">
+        <v>80</v>
+      </c>
+      <c r="G44">
+        <v>81</v>
+      </c>
+      <c r="H44">
+        <v>82</v>
+      </c>
+      <c r="I44">
+        <v>83</v>
+      </c>
+      <c r="J44">
+        <v>84</v>
+      </c>
+      <c r="K44">
+        <v>85</v>
+      </c>
+      <c r="L44">
+        <v>86</v>
+      </c>
+      <c r="M44">
+        <v>87</v>
+      </c>
+      <c r="N44">
+        <v>32</v>
+      </c>
+      <c r="O44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15">
+      <c r="A45" t="s">
+        <v>19</v>
+      </c>
+      <c r="B45">
+        <v>8</v>
+      </c>
+      <c r="C45">
+        <v>2</v>
+      </c>
+      <c r="D45">
+        <v>20</v>
+      </c>
+      <c r="E45">
+        <v>31</v>
+      </c>
+      <c r="F45">
+        <v>90</v>
+      </c>
+      <c r="G45">
+        <v>91</v>
+      </c>
+      <c r="H45">
+        <v>92</v>
+      </c>
+      <c r="I45">
+        <v>93</v>
+      </c>
+      <c r="J45">
+        <v>94</v>
+      </c>
+      <c r="K45">
+        <v>95</v>
+      </c>
+      <c r="L45">
+        <v>96</v>
+      </c>
+      <c r="M45">
+        <v>97</v>
+      </c>
+      <c r="N45">
+        <v>64</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15">
+      <c r="A46" t="s">
+        <v>19</v>
+      </c>
+      <c r="B46">
+        <v>8</v>
+      </c>
+      <c r="C46">
+        <v>3</v>
+      </c>
+      <c r="D46">
+        <v>30</v>
+      </c>
+      <c r="E46">
+        <v>40</v>
+      </c>
+      <c r="F46" t="s">
+        <v>21</v>
+      </c>
+      <c r="G46" t="s">
+        <v>22</v>
+      </c>
+      <c r="H46" t="s">
+        <v>23</v>
+      </c>
+      <c r="I46" t="s">
+        <v>24</v>
+      </c>
+      <c r="J46" t="s">
+        <v>25</v>
+      </c>
+      <c r="K46" t="s">
+        <v>26</v>
+      </c>
+      <c r="L46">
+        <v>12</v>
+      </c>
+      <c r="M46">
+        <v>34</v>
+      </c>
+      <c r="N46" t="s">
+        <v>27</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15">
+      <c r="A47" t="s">
+        <v>19</v>
+      </c>
+      <c r="B47">
+        <v>8</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+      <c r="D47">
+        <v>10</v>
+      </c>
+      <c r="E47">
+        <v>20</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>1</v>
+      </c>
+      <c r="H47">
+        <v>2</v>
+      </c>
+      <c r="I47">
+        <v>3</v>
+      </c>
+      <c r="J47">
+        <v>4</v>
+      </c>
+      <c r="K47">
+        <v>5</v>
+      </c>
+      <c r="L47">
+        <v>6</v>
+      </c>
+      <c r="M47">
+        <v>7</v>
+      </c>
+      <c r="N47" t="s">
+        <v>20</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15">
+      <c r="A48" t="s">
+        <v>19</v>
+      </c>
+      <c r="B48">
+        <v>8</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
+      <c r="D48">
+        <v>10</v>
+      </c>
+      <c r="E48">
+        <v>21</v>
+      </c>
+      <c r="F48">
+        <v>10</v>
+      </c>
+      <c r="G48">
+        <v>11</v>
+      </c>
+      <c r="H48">
+        <v>12</v>
+      </c>
+      <c r="I48">
+        <v>13</v>
+      </c>
+      <c r="J48">
+        <v>14</v>
+      </c>
+      <c r="K48">
+        <v>15</v>
+      </c>
+      <c r="L48">
+        <v>16</v>
+      </c>
+      <c r="M48">
+        <v>17</v>
+      </c>
+      <c r="N48">
+        <v>14</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15">
+      <c r="A49" t="s">
+        <v>19</v>
+      </c>
+      <c r="B49">
+        <v>8</v>
+      </c>
+      <c r="C49">
+        <v>2</v>
+      </c>
+      <c r="D49">
+        <v>20</v>
+      </c>
+      <c r="E49">
+        <v>30</v>
+      </c>
+      <c r="F49">
+        <v>80</v>
+      </c>
+      <c r="G49">
+        <v>81</v>
+      </c>
+      <c r="H49">
+        <v>82</v>
+      </c>
+      <c r="I49">
+        <v>83</v>
+      </c>
+      <c r="J49">
+        <v>84</v>
+      </c>
+      <c r="K49">
+        <v>85</v>
+      </c>
+      <c r="L49">
+        <v>86</v>
+      </c>
+      <c r="M49">
+        <v>87</v>
+      </c>
+      <c r="N49">
+        <v>32</v>
+      </c>
+      <c r="O49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15">
+      <c r="A50" t="s">
+        <v>19</v>
+      </c>
+      <c r="B50">
+        <v>8</v>
+      </c>
+      <c r="C50">
+        <v>2</v>
+      </c>
+      <c r="D50">
+        <v>20</v>
+      </c>
+      <c r="E50">
+        <v>31</v>
+      </c>
+      <c r="F50">
+        <v>90</v>
+      </c>
+      <c r="G50">
+        <v>91</v>
+      </c>
+      <c r="H50">
+        <v>92</v>
+      </c>
+      <c r="I50">
+        <v>93</v>
+      </c>
+      <c r="J50">
+        <v>94</v>
+      </c>
+      <c r="K50">
+        <v>95</v>
+      </c>
+      <c r="L50">
+        <v>96</v>
+      </c>
+      <c r="M50">
+        <v>97</v>
+      </c>
+      <c r="N50">
+        <v>64</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15">
+      <c r="A51" t="s">
+        <v>19</v>
+      </c>
+      <c r="B51">
+        <v>8</v>
+      </c>
+      <c r="C51">
+        <v>3</v>
+      </c>
+      <c r="D51">
+        <v>30</v>
+      </c>
+      <c r="E51">
+        <v>40</v>
+      </c>
+      <c r="F51" t="s">
+        <v>21</v>
+      </c>
+      <c r="G51" t="s">
+        <v>22</v>
+      </c>
+      <c r="H51" t="s">
+        <v>23</v>
+      </c>
+      <c r="I51" t="s">
+        <v>24</v>
+      </c>
+      <c r="J51" t="s">
+        <v>25</v>
+      </c>
+      <c r="K51" t="s">
+        <v>26</v>
+      </c>
+      <c r="L51">
+        <v>12</v>
+      </c>
+      <c r="M51">
+        <v>34</v>
+      </c>
+      <c r="N51" t="s">
+        <v>27</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15">
+      <c r="A52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B52">
+        <v>8</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+      <c r="D52">
+        <v>10</v>
+      </c>
+      <c r="E52">
+        <v>20</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>1</v>
+      </c>
+      <c r="H52">
+        <v>2</v>
+      </c>
+      <c r="I52">
+        <v>3</v>
+      </c>
+      <c r="J52">
+        <v>4</v>
+      </c>
+      <c r="K52">
+        <v>5</v>
+      </c>
+      <c r="L52">
+        <v>6</v>
+      </c>
+      <c r="M52">
+        <v>7</v>
+      </c>
+      <c r="N52" t="s">
+        <v>20</v>
+      </c>
+      <c r="O52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15">
+      <c r="A53" t="s">
+        <v>19</v>
+      </c>
+      <c r="B53">
+        <v>8</v>
+      </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
+      <c r="D53">
+        <v>10</v>
+      </c>
+      <c r="E53">
+        <v>21</v>
+      </c>
+      <c r="F53">
+        <v>10</v>
+      </c>
+      <c r="G53">
+        <v>11</v>
+      </c>
+      <c r="H53">
+        <v>12</v>
+      </c>
+      <c r="I53">
+        <v>13</v>
+      </c>
+      <c r="J53">
+        <v>14</v>
+      </c>
+      <c r="K53">
+        <v>15</v>
+      </c>
+      <c r="L53">
+        <v>16</v>
+      </c>
+      <c r="M53">
+        <v>17</v>
+      </c>
+      <c r="N53">
+        <v>14</v>
+      </c>
+      <c r="O53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15">
+      <c r="A54" t="s">
+        <v>19</v>
+      </c>
+      <c r="B54">
+        <v>8</v>
+      </c>
+      <c r="C54">
+        <v>2</v>
+      </c>
+      <c r="D54">
+        <v>20</v>
+      </c>
+      <c r="E54">
+        <v>30</v>
+      </c>
+      <c r="F54">
+        <v>80</v>
+      </c>
+      <c r="G54">
+        <v>81</v>
+      </c>
+      <c r="H54">
+        <v>82</v>
+      </c>
+      <c r="I54">
+        <v>83</v>
+      </c>
+      <c r="J54">
+        <v>84</v>
+      </c>
+      <c r="K54">
+        <v>85</v>
+      </c>
+      <c r="L54">
+        <v>86</v>
+      </c>
+      <c r="M54">
+        <v>87</v>
+      </c>
+      <c r="N54">
+        <v>32</v>
+      </c>
+      <c r="O54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15">
+      <c r="A55" t="s">
+        <v>19</v>
+      </c>
+      <c r="B55">
+        <v>8</v>
+      </c>
+      <c r="C55">
+        <v>2</v>
+      </c>
+      <c r="D55">
+        <v>20</v>
+      </c>
+      <c r="E55">
+        <v>31</v>
+      </c>
+      <c r="F55">
+        <v>90</v>
+      </c>
+      <c r="G55">
+        <v>91</v>
+      </c>
+      <c r="H55">
+        <v>92</v>
+      </c>
+      <c r="I55">
+        <v>93</v>
+      </c>
+      <c r="J55">
+        <v>94</v>
+      </c>
+      <c r="K55">
+        <v>95</v>
+      </c>
+      <c r="L55">
+        <v>96</v>
+      </c>
+      <c r="M55">
+        <v>97</v>
+      </c>
+      <c r="N55">
+        <v>64</v>
+      </c>
+      <c r="O55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15">
+      <c r="A56" t="s">
+        <v>19</v>
+      </c>
+      <c r="B56">
+        <v>8</v>
+      </c>
+      <c r="C56">
+        <v>3</v>
+      </c>
+      <c r="D56">
+        <v>30</v>
+      </c>
+      <c r="E56">
+        <v>40</v>
+      </c>
+      <c r="F56" t="s">
+        <v>21</v>
+      </c>
+      <c r="G56" t="s">
+        <v>22</v>
+      </c>
+      <c r="H56" t="s">
+        <v>23</v>
+      </c>
+      <c r="I56" t="s">
+        <v>24</v>
+      </c>
+      <c r="J56" t="s">
+        <v>25</v>
+      </c>
+      <c r="K56" t="s">
+        <v>26</v>
+      </c>
+      <c r="L56">
+        <v>12</v>
+      </c>
+      <c r="M56">
+        <v>34</v>
+      </c>
+      <c r="N56" t="s">
+        <v>27</v>
+      </c>
+      <c r="O56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15">
+      <c r="A57" t="s">
+        <v>19</v>
+      </c>
+      <c r="B57">
+        <v>8</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
+      <c r="D57">
+        <v>10</v>
+      </c>
+      <c r="E57">
+        <v>20</v>
+      </c>
+      <c r="F57">
+        <v>0</v>
+      </c>
+      <c r="G57">
+        <v>1</v>
+      </c>
+      <c r="H57">
+        <v>2</v>
+      </c>
+      <c r="I57">
+        <v>3</v>
+      </c>
+      <c r="J57">
+        <v>4</v>
+      </c>
+      <c r="K57">
+        <v>5</v>
+      </c>
+      <c r="L57">
+        <v>6</v>
+      </c>
+      <c r="M57">
+        <v>7</v>
+      </c>
+      <c r="N57" t="s">
+        <v>20</v>
+      </c>
+      <c r="O57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15">
+      <c r="A58" t="s">
+        <v>19</v>
+      </c>
+      <c r="B58">
+        <v>8</v>
+      </c>
+      <c r="C58">
+        <v>1</v>
+      </c>
+      <c r="D58">
+        <v>10</v>
+      </c>
+      <c r="E58">
+        <v>21</v>
+      </c>
+      <c r="F58">
+        <v>10</v>
+      </c>
+      <c r="G58">
+        <v>11</v>
+      </c>
+      <c r="H58">
+        <v>12</v>
+      </c>
+      <c r="I58">
+        <v>13</v>
+      </c>
+      <c r="J58">
+        <v>14</v>
+      </c>
+      <c r="K58">
+        <v>15</v>
+      </c>
+      <c r="L58">
+        <v>16</v>
+      </c>
+      <c r="M58">
+        <v>17</v>
+      </c>
+      <c r="N58">
+        <v>14</v>
+      </c>
+      <c r="O58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15">
+      <c r="A59" t="s">
+        <v>19</v>
+      </c>
+      <c r="B59">
+        <v>8</v>
+      </c>
+      <c r="C59">
+        <v>2</v>
+      </c>
+      <c r="D59">
+        <v>20</v>
+      </c>
+      <c r="E59">
+        <v>30</v>
+      </c>
+      <c r="F59">
+        <v>80</v>
+      </c>
+      <c r="G59">
+        <v>81</v>
+      </c>
+      <c r="H59">
+        <v>82</v>
+      </c>
+      <c r="I59">
+        <v>83</v>
+      </c>
+      <c r="J59">
+        <v>84</v>
+      </c>
+      <c r="K59">
+        <v>85</v>
+      </c>
+      <c r="L59">
+        <v>86</v>
+      </c>
+      <c r="M59">
+        <v>87</v>
+      </c>
+      <c r="N59">
+        <v>32</v>
+      </c>
+      <c r="O59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15">
+      <c r="A60" t="s">
+        <v>19</v>
+      </c>
+      <c r="B60">
+        <v>8</v>
+      </c>
+      <c r="C60">
+        <v>2</v>
+      </c>
+      <c r="D60">
+        <v>20</v>
+      </c>
+      <c r="E60">
+        <v>31</v>
+      </c>
+      <c r="F60">
+        <v>90</v>
+      </c>
+      <c r="G60">
+        <v>91</v>
+      </c>
+      <c r="H60">
+        <v>92</v>
+      </c>
+      <c r="I60">
+        <v>93</v>
+      </c>
+      <c r="J60">
+        <v>94</v>
+      </c>
+      <c r="K60">
+        <v>95</v>
+      </c>
+      <c r="L60">
+        <v>96</v>
+      </c>
+      <c r="M60">
+        <v>97</v>
+      </c>
+      <c r="N60">
+        <v>64</v>
+      </c>
+      <c r="O60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15">
+      <c r="A61" t="s">
+        <v>19</v>
+      </c>
+      <c r="B61">
+        <v>8</v>
+      </c>
+      <c r="C61">
+        <v>3</v>
+      </c>
+      <c r="D61">
+        <v>30</v>
+      </c>
+      <c r="E61">
+        <v>40</v>
+      </c>
+      <c r="F61" t="s">
+        <v>21</v>
+      </c>
+      <c r="G61" t="s">
+        <v>22</v>
+      </c>
+      <c r="H61" t="s">
+        <v>23</v>
+      </c>
+      <c r="I61" t="s">
+        <v>24</v>
+      </c>
+      <c r="J61" t="s">
+        <v>25</v>
+      </c>
+      <c r="K61" t="s">
+        <v>26</v>
+      </c>
+      <c r="L61">
+        <v>12</v>
+      </c>
+      <c r="M61">
+        <v>34</v>
+      </c>
+      <c r="N61" t="s">
+        <v>27</v>
+      </c>
+      <c r="O61">
         <v>0</v>
       </c>
     </row>

--- a/mass_production_tool/value_test_sample.xlsx
+++ b/mass_production_tool/value_test_sample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\Mass_produc\mass_produc\mass_production_tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70369499-BE07-45AD-A22D-4F0A417781BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3682DA2F-3F52-4CDD-AD1E-E8B69BCE7FED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8880" yWindow="6600" windowWidth="34560" windowHeight="18600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="46296" windowHeight="25416" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ValueTest" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="29">
   <si>
     <t>HDR</t>
   </si>
@@ -104,6 +104,10 @@
   </si>
   <si>
     <t>C8</t>
+  </si>
+  <si>
+    <t>EXCPECTED</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -316,10 +320,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S61"/>
+  <dimension ref="A1:T61"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="1" width="13.19921875" customWidth="1"/>
+    <col min="14" max="14" width="17.296875" customWidth="1"/>
+    <col min="15" max="16" width="18.5" customWidth="1"/>
+    <col min="17" max="17" width="16.3984375" customWidth="1"/>
+    <col min="18" max="18" width="16.296875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:20">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -363,22 +374,25 @@
         <v>13</v>
       </c>
       <c r="O1" t="s">
+        <v>28</v>
+      </c>
+      <c r="P1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:20">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -424,8 +438,11 @@
       <c r="O2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:19">
+      <c r="P2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -471,8 +488,11 @@
       <c r="O3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:19">
+      <c r="P3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -518,8 +538,11 @@
       <c r="O4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:19">
+      <c r="P4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -565,8 +588,11 @@
       <c r="O5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:19">
+      <c r="P5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -612,8 +638,11 @@
       <c r="O6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:19">
+      <c r="P6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -659,8 +688,11 @@
       <c r="O7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:19">
+      <c r="P7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -706,8 +738,11 @@
       <c r="O8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:19">
+      <c r="P8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -753,8 +788,11 @@
       <c r="O9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:19">
+      <c r="P9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -800,8 +838,11 @@
       <c r="O10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:19">
+      <c r="P10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -847,8 +888,11 @@
       <c r="O11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:19">
+      <c r="P11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -894,8 +938,11 @@
       <c r="O12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:19">
+      <c r="P12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -941,8 +988,11 @@
       <c r="O13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19">
+      <c r="P13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -988,8 +1038,11 @@
       <c r="O14">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:19">
+      <c r="P14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -1035,8 +1088,11 @@
       <c r="O15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19">
+      <c r="P15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -1082,8 +1138,11 @@
       <c r="O16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:15">
+      <c r="P16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -1129,8 +1188,11 @@
       <c r="O17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:15">
+      <c r="P17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -1176,8 +1238,11 @@
       <c r="O18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:15">
+      <c r="P18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -1223,8 +1288,11 @@
       <c r="O19">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:15">
+      <c r="P19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -1270,8 +1338,11 @@
       <c r="O20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:15">
+      <c r="P20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -1317,8 +1388,11 @@
       <c r="O21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:15">
+      <c r="P21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
       <c r="A22" t="s">
         <v>19</v>
       </c>
@@ -1364,8 +1438,11 @@
       <c r="O22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:15">
+      <c r="P22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
       <c r="A23" t="s">
         <v>19</v>
       </c>
@@ -1411,8 +1488,11 @@
       <c r="O23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:15">
+      <c r="P23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
       <c r="A24" t="s">
         <v>19</v>
       </c>
@@ -1458,8 +1538,11 @@
       <c r="O24">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:15">
+      <c r="P24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
       <c r="A25" t="s">
         <v>19</v>
       </c>
@@ -1505,8 +1588,11 @@
       <c r="O25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:15">
+      <c r="P25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
       <c r="A26" t="s">
         <v>19</v>
       </c>
@@ -1552,8 +1638,11 @@
       <c r="O26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:15">
+      <c r="P26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16">
       <c r="A27" t="s">
         <v>19</v>
       </c>
@@ -1599,8 +1688,11 @@
       <c r="O27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:15">
+      <c r="P27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16">
       <c r="A28" t="s">
         <v>19</v>
       </c>
@@ -1646,8 +1738,11 @@
       <c r="O28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:15">
+      <c r="P28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
       <c r="A29" t="s">
         <v>19</v>
       </c>
@@ -1693,8 +1788,11 @@
       <c r="O29">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:15">
+      <c r="P29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16">
       <c r="A30" t="s">
         <v>19</v>
       </c>
@@ -1740,8 +1838,11 @@
       <c r="O30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:15">
+      <c r="P30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16">
       <c r="A31" t="s">
         <v>19</v>
       </c>
@@ -1787,8 +1888,11 @@
       <c r="O31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:15">
+      <c r="P31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16">
       <c r="A32" t="s">
         <v>19</v>
       </c>
@@ -1834,8 +1938,11 @@
       <c r="O32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:15">
+      <c r="P32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16">
       <c r="A33" t="s">
         <v>19</v>
       </c>
@@ -1881,8 +1988,11 @@
       <c r="O33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:15">
+      <c r="P33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16">
       <c r="A34" t="s">
         <v>19</v>
       </c>
@@ -1928,8 +2038,11 @@
       <c r="O34">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:15">
+      <c r="P34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16">
       <c r="A35" t="s">
         <v>19</v>
       </c>
@@ -1975,8 +2088,11 @@
       <c r="O35">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:15">
+      <c r="P35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16">
       <c r="A36" t="s">
         <v>19</v>
       </c>
@@ -2022,8 +2138,11 @@
       <c r="O36">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:15">
+      <c r="P36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16">
       <c r="A37" t="s">
         <v>19</v>
       </c>
@@ -2069,8 +2188,11 @@
       <c r="O37">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:15">
+      <c r="P37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16">
       <c r="A38" t="s">
         <v>19</v>
       </c>
@@ -2116,8 +2238,11 @@
       <c r="O38">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:15">
+      <c r="P38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16">
       <c r="A39" t="s">
         <v>19</v>
       </c>
@@ -2163,8 +2288,11 @@
       <c r="O39">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:15">
+      <c r="P39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16">
       <c r="A40" t="s">
         <v>19</v>
       </c>
@@ -2210,8 +2338,11 @@
       <c r="O40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:15">
+      <c r="P40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16">
       <c r="A41" t="s">
         <v>19</v>
       </c>
@@ -2257,8 +2388,11 @@
       <c r="O41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:15">
+      <c r="P41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16">
       <c r="A42" t="s">
         <v>19</v>
       </c>
@@ -2304,8 +2438,11 @@
       <c r="O42">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:15">
+      <c r="P42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16">
       <c r="A43" t="s">
         <v>19</v>
       </c>
@@ -2351,8 +2488,11 @@
       <c r="O43">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:15">
+      <c r="P43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16">
       <c r="A44" t="s">
         <v>19</v>
       </c>
@@ -2398,8 +2538,11 @@
       <c r="O44">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:15">
+      <c r="P44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16">
       <c r="A45" t="s">
         <v>19</v>
       </c>
@@ -2445,8 +2588,11 @@
       <c r="O45">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:15">
+      <c r="P45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16">
       <c r="A46" t="s">
         <v>19</v>
       </c>
@@ -2492,8 +2638,11 @@
       <c r="O46">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:15">
+      <c r="P46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
       <c r="A47" t="s">
         <v>19</v>
       </c>
@@ -2539,8 +2688,11 @@
       <c r="O47">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:15">
+      <c r="P47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16">
       <c r="A48" t="s">
         <v>19</v>
       </c>
@@ -2586,8 +2738,11 @@
       <c r="O48">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:15">
+      <c r="P48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16">
       <c r="A49" t="s">
         <v>19</v>
       </c>
@@ -2633,8 +2788,11 @@
       <c r="O49">
         <v>1</v>
       </c>
-    </row>
-    <row r="50" spans="1:15">
+      <c r="P49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16">
       <c r="A50" t="s">
         <v>19</v>
       </c>
@@ -2680,8 +2838,11 @@
       <c r="O50">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:15">
+      <c r="P50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16">
       <c r="A51" t="s">
         <v>19</v>
       </c>
@@ -2727,8 +2888,11 @@
       <c r="O51">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:15">
+      <c r="P51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16">
       <c r="A52" t="s">
         <v>19</v>
       </c>
@@ -2774,8 +2938,11 @@
       <c r="O52">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:15">
+      <c r="P52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16">
       <c r="A53" t="s">
         <v>19</v>
       </c>
@@ -2821,8 +2988,11 @@
       <c r="O53">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:15">
+      <c r="P53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16">
       <c r="A54" t="s">
         <v>19</v>
       </c>
@@ -2868,8 +3038,11 @@
       <c r="O54">
         <v>1</v>
       </c>
-    </row>
-    <row r="55" spans="1:15">
+      <c r="P54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16">
       <c r="A55" t="s">
         <v>19</v>
       </c>
@@ -2915,8 +3088,11 @@
       <c r="O55">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:15">
+      <c r="P55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16">
       <c r="A56" t="s">
         <v>19</v>
       </c>
@@ -2962,8 +3138,11 @@
       <c r="O56">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:15">
+      <c r="P56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16">
       <c r="A57" t="s">
         <v>19</v>
       </c>
@@ -3009,8 +3188,11 @@
       <c r="O57">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:15">
+      <c r="P57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16">
       <c r="A58" t="s">
         <v>19</v>
       </c>
@@ -3056,8 +3238,11 @@
       <c r="O58">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:15">
+      <c r="P58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16">
       <c r="A59" t="s">
         <v>19</v>
       </c>
@@ -3103,8 +3288,11 @@
       <c r="O59">
         <v>1</v>
       </c>
-    </row>
-    <row r="60" spans="1:15">
+      <c r="P59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16">
       <c r="A60" t="s">
         <v>19</v>
       </c>
@@ -3150,8 +3338,11 @@
       <c r="O60">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:15">
+      <c r="P60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16">
       <c r="A61" t="s">
         <v>19</v>
       </c>
@@ -3195,6 +3386,9 @@
         <v>27</v>
       </c>
       <c r="O61">
+        <v>0</v>
+      </c>
+      <c r="P61">
         <v>0</v>
       </c>
     </row>

--- a/mass_production_tool/value_test_sample.xlsx
+++ b/mass_production_tool/value_test_sample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\Mass_produc\mass_produc\mass_production_tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3682DA2F-3F52-4CDD-AD1E-E8B69BCE7FED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFAE6F87-15AF-4AA0-B125-ECB03418DE49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="46296" windowHeight="25416" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11460" yWindow="8856" windowWidth="28716" windowHeight="15504" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ValueTest" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="29">
   <si>
     <t>HDR</t>
   </si>
@@ -106,7 +106,7 @@
     <t>C8</t>
   </si>
   <si>
-    <t>EXCPECTED</t>
+    <t>EXPECTED</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -158,7 +158,18 @@
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -328,6 +339,7 @@
     <col min="15" max="16" width="18.5" customWidth="1"/>
     <col min="17" max="17" width="16.3984375" customWidth="1"/>
     <col min="18" max="18" width="16.296875" customWidth="1"/>
+    <col min="19" max="19" width="16.09765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
@@ -435,8 +447,8 @@
       <c r="N2" t="s">
         <v>20</v>
       </c>
-      <c r="O2">
-        <v>0</v>
+      <c r="O2" t="s">
+        <v>20</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -486,7 +498,7 @@
         <v>14</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="P3">
         <v>0</v>
@@ -536,7 +548,7 @@
         <v>32</v>
       </c>
       <c r="O4">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="P4">
         <v>1</v>
@@ -586,7 +598,7 @@
         <v>64</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -635,8 +647,8 @@
       <c r="N6" t="s">
         <v>27</v>
       </c>
-      <c r="O6">
-        <v>0</v>
+      <c r="O6" t="s">
+        <v>27</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -685,8 +697,8 @@
       <c r="N7" t="s">
         <v>20</v>
       </c>
-      <c r="O7">
-        <v>0</v>
+      <c r="O7" t="s">
+        <v>20</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -736,7 +748,7 @@
         <v>14</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -786,7 +798,7 @@
         <v>32</v>
       </c>
       <c r="O9">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="P9">
         <v>1</v>
@@ -836,7 +848,7 @@
         <v>64</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="P10">
         <v>0</v>
@@ -885,8 +897,8 @@
       <c r="N11" t="s">
         <v>27</v>
       </c>
-      <c r="O11">
-        <v>0</v>
+      <c r="O11" t="s">
+        <v>27</v>
       </c>
       <c r="P11">
         <v>0</v>
@@ -935,8 +947,8 @@
       <c r="N12" t="s">
         <v>20</v>
       </c>
-      <c r="O12">
-        <v>0</v>
+      <c r="O12" t="s">
+        <v>20</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -986,7 +998,7 @@
         <v>14</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -1036,7 +1048,7 @@
         <v>32</v>
       </c>
       <c r="O14">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="P14">
         <v>1</v>
@@ -1086,7 +1098,7 @@
         <v>64</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -1135,8 +1147,8 @@
       <c r="N16" t="s">
         <v>27</v>
       </c>
-      <c r="O16">
-        <v>0</v>
+      <c r="O16" t="s">
+        <v>27</v>
       </c>
       <c r="P16">
         <v>0</v>
@@ -1185,8 +1197,8 @@
       <c r="N17" t="s">
         <v>20</v>
       </c>
-      <c r="O17">
-        <v>0</v>
+      <c r="O17" t="s">
+        <v>20</v>
       </c>
       <c r="P17">
         <v>0</v>
@@ -1236,7 +1248,7 @@
         <v>14</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -1286,7 +1298,7 @@
         <v>32</v>
       </c>
       <c r="O19">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="P19">
         <v>1</v>
@@ -1336,7 +1348,7 @@
         <v>64</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="P20">
         <v>0</v>
@@ -1385,8 +1397,8 @@
       <c r="N21" t="s">
         <v>27</v>
       </c>
-      <c r="O21">
-        <v>0</v>
+      <c r="O21" t="s">
+        <v>27</v>
       </c>
       <c r="P21">
         <v>0</v>
@@ -1435,8 +1447,8 @@
       <c r="N22" t="s">
         <v>20</v>
       </c>
-      <c r="O22">
-        <v>0</v>
+      <c r="O22" t="s">
+        <v>20</v>
       </c>
       <c r="P22">
         <v>0</v>
@@ -1486,7 +1498,7 @@
         <v>14</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="P23">
         <v>0</v>
@@ -1536,7 +1548,7 @@
         <v>32</v>
       </c>
       <c r="O24">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="P24">
         <v>1</v>
@@ -1586,7 +1598,7 @@
         <v>64</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="P25">
         <v>0</v>
@@ -1635,8 +1647,8 @@
       <c r="N26" t="s">
         <v>27</v>
       </c>
-      <c r="O26">
-        <v>0</v>
+      <c r="O26" t="s">
+        <v>27</v>
       </c>
       <c r="P26">
         <v>0</v>
@@ -1685,8 +1697,8 @@
       <c r="N27" t="s">
         <v>20</v>
       </c>
-      <c r="O27">
-        <v>0</v>
+      <c r="O27" t="s">
+        <v>20</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -1736,7 +1748,7 @@
         <v>14</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -1786,7 +1798,7 @@
         <v>32</v>
       </c>
       <c r="O29">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="P29">
         <v>1</v>
@@ -1836,7 +1848,7 @@
         <v>64</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="P30">
         <v>0</v>
@@ -1885,8 +1897,8 @@
       <c r="N31" t="s">
         <v>27</v>
       </c>
-      <c r="O31">
-        <v>0</v>
+      <c r="O31" t="s">
+        <v>27</v>
       </c>
       <c r="P31">
         <v>0</v>
@@ -1935,8 +1947,8 @@
       <c r="N32" t="s">
         <v>20</v>
       </c>
-      <c r="O32">
-        <v>0</v>
+      <c r="O32" t="s">
+        <v>20</v>
       </c>
       <c r="P32">
         <v>0</v>
@@ -1986,7 +1998,7 @@
         <v>14</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="P33">
         <v>0</v>
@@ -2036,7 +2048,7 @@
         <v>32</v>
       </c>
       <c r="O34">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="P34">
         <v>1</v>
@@ -2086,7 +2098,7 @@
         <v>64</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="P35">
         <v>0</v>
@@ -2135,8 +2147,8 @@
       <c r="N36" t="s">
         <v>27</v>
       </c>
-      <c r="O36">
-        <v>0</v>
+      <c r="O36" t="s">
+        <v>27</v>
       </c>
       <c r="P36">
         <v>0</v>
@@ -2185,8 +2197,8 @@
       <c r="N37" t="s">
         <v>20</v>
       </c>
-      <c r="O37">
-        <v>0</v>
+      <c r="O37" t="s">
+        <v>20</v>
       </c>
       <c r="P37">
         <v>0</v>
@@ -2236,7 +2248,7 @@
         <v>14</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="P38">
         <v>0</v>
@@ -2286,7 +2298,7 @@
         <v>32</v>
       </c>
       <c r="O39">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="P39">
         <v>1</v>
@@ -2336,7 +2348,7 @@
         <v>64</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="P40">
         <v>0</v>
@@ -2385,8 +2397,8 @@
       <c r="N41" t="s">
         <v>27</v>
       </c>
-      <c r="O41">
-        <v>0</v>
+      <c r="O41" t="s">
+        <v>27</v>
       </c>
       <c r="P41">
         <v>0</v>
@@ -2435,8 +2447,8 @@
       <c r="N42" t="s">
         <v>20</v>
       </c>
-      <c r="O42">
-        <v>0</v>
+      <c r="O42" t="s">
+        <v>20</v>
       </c>
       <c r="P42">
         <v>0</v>
@@ -2486,7 +2498,7 @@
         <v>14</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="P43">
         <v>0</v>
@@ -2536,7 +2548,7 @@
         <v>32</v>
       </c>
       <c r="O44">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="P44">
         <v>1</v>
@@ -2586,7 +2598,7 @@
         <v>64</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="P45">
         <v>0</v>
@@ -2635,8 +2647,8 @@
       <c r="N46" t="s">
         <v>27</v>
       </c>
-      <c r="O46">
-        <v>0</v>
+      <c r="O46" t="s">
+        <v>27</v>
       </c>
       <c r="P46">
         <v>0</v>
@@ -2685,8 +2697,8 @@
       <c r="N47" t="s">
         <v>20</v>
       </c>
-      <c r="O47">
-        <v>0</v>
+      <c r="O47" t="s">
+        <v>20</v>
       </c>
       <c r="P47">
         <v>0</v>
@@ -2736,7 +2748,7 @@
         <v>14</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="P48">
         <v>0</v>
@@ -2786,7 +2798,7 @@
         <v>32</v>
       </c>
       <c r="O49">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="P49">
         <v>1</v>
@@ -2836,7 +2848,7 @@
         <v>64</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="P50">
         <v>0</v>
@@ -2885,8 +2897,8 @@
       <c r="N51" t="s">
         <v>27</v>
       </c>
-      <c r="O51">
-        <v>0</v>
+      <c r="O51" t="s">
+        <v>27</v>
       </c>
       <c r="P51">
         <v>0</v>
@@ -2935,8 +2947,8 @@
       <c r="N52" t="s">
         <v>20</v>
       </c>
-      <c r="O52">
-        <v>0</v>
+      <c r="O52" t="s">
+        <v>20</v>
       </c>
       <c r="P52">
         <v>0</v>
@@ -2986,7 +2998,7 @@
         <v>14</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="P53">
         <v>0</v>
@@ -3036,7 +3048,7 @@
         <v>32</v>
       </c>
       <c r="O54">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="P54">
         <v>1</v>
@@ -3086,7 +3098,7 @@
         <v>64</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="P55">
         <v>0</v>
@@ -3135,8 +3147,8 @@
       <c r="N56" t="s">
         <v>27</v>
       </c>
-      <c r="O56">
-        <v>0</v>
+      <c r="O56" t="s">
+        <v>27</v>
       </c>
       <c r="P56">
         <v>0</v>
@@ -3185,8 +3197,8 @@
       <c r="N57" t="s">
         <v>20</v>
       </c>
-      <c r="O57">
-        <v>0</v>
+      <c r="O57" t="s">
+        <v>20</v>
       </c>
       <c r="P57">
         <v>0</v>
@@ -3236,7 +3248,7 @@
         <v>14</v>
       </c>
       <c r="O58">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="P58">
         <v>0</v>
@@ -3286,7 +3298,7 @@
         <v>32</v>
       </c>
       <c r="O59">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="P59">
         <v>1</v>
@@ -3336,7 +3348,7 @@
         <v>64</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="P60">
         <v>0</v>
@@ -3385,8 +3397,8 @@
       <c r="N61" t="s">
         <v>27</v>
       </c>
-      <c r="O61">
-        <v>0</v>
+      <c r="O61" t="s">
+        <v>27</v>
       </c>
       <c r="P61">
         <v>0</v>
@@ -3394,6 +3406,9 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
+  <conditionalFormatting sqref="L1:N1">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>